--- a/output/基础户升降级明细.xlsx
+++ b/output/基础户升降级明细.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,177 +433,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧时点</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧基础户标识</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>旧有效户标识</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>新基础户标识</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>新有效户标识</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>账户销户</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_标识</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_标识</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_年日均</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_年日均</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_标识</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_标识</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_年日均</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_年日均</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>预计年日均</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>预警基础户</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>预警有效户</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>基础户临界</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>有效户临界</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户达标</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户达标</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户保持</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户保持</t>
         </is>
@@ -69143,57 +69155,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>账户销户</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_标识</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
@@ -69301,57 +69313,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>账户销户</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
@@ -70785,52 +70797,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_标识</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
@@ -70851,52 +70863,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_年日均</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>

--- a/output/基础户升降级明细.xlsx
+++ b/output/基础户升降级明细.xlsx
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>刘羽佳</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -32585,7 +32585,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -35902,7 +35902,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -36009,7 +36009,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -36330,7 +36330,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -38256,7 +38256,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -39968,7 +39968,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -40396,7 +40396,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -41359,7 +41359,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -41894,7 +41894,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -42201,7 +42201,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -42950,7 +42950,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -43271,7 +43271,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -43378,7 +43378,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -44020,7 +44020,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -45076,7 +45076,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D418" t="n">
@@ -45504,7 +45504,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -45825,7 +45825,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -46146,7 +46146,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -46253,7 +46253,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D429" t="n">
@@ -46360,7 +46360,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -46895,7 +46895,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -47430,7 +47430,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -47965,7 +47965,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -48500,7 +48500,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -48928,7 +48928,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -49998,7 +49998,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -50105,7 +50105,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -50426,7 +50426,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -50640,7 +50640,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D470" t="n">
@@ -50854,7 +50854,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -51603,7 +51603,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -51817,7 +51817,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -52031,7 +52031,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -52352,7 +52352,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -53422,7 +53422,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -53529,7 +53529,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -53636,7 +53636,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -55027,7 +55027,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D511" t="n">
@@ -55241,7 +55241,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -55348,7 +55348,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D514" t="n">
@@ -56311,7 +56311,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D523" t="n">
@@ -56525,7 +56525,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -57595,7 +57595,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D535" t="n">
@@ -57702,7 +57702,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D537" t="n">
@@ -58237,7 +58237,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -58558,7 +58558,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D544" t="n">
@@ -59628,7 +59628,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D554" t="n">
@@ -59735,7 +59735,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -59842,7 +59842,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -59949,7 +59949,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D557" t="n">
@@ -60056,7 +60056,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D558" t="n">
@@ -60163,7 +60163,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D559" t="n">
@@ -61019,7 +61019,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D567" t="n">
@@ -61768,7 +61768,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D574" t="n">
@@ -61875,7 +61875,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D575" t="n">
@@ -63159,7 +63159,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D587" t="n">
@@ -63373,7 +63373,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D589" t="n">
@@ -63587,7 +63587,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D591" t="n">
@@ -64015,7 +64015,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D595" t="n">
@@ -64122,7 +64122,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D596" t="n">
@@ -65299,7 +65299,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D607" t="n">
@@ -67760,7 +67760,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D630" t="n">
@@ -69450,7 +69450,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>河北金怡化纤有限公司</t>
+          <t>河北仁恒工程管理服务有限公司</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -69465,31 +69465,31 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>141747.53</v>
+        <v>172758.08</v>
       </c>
       <c r="F4" t="n">
-        <v>69702.14</v>
+        <v>82215.39999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>977.5</v>
+        <v>82952.86</v>
       </c>
       <c r="H4" t="n">
-        <v>112</v>
+        <v>264</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>421107.52</v>
+        <v>251539.34</v>
       </c>
       <c r="K4" t="n">
-        <v>4061107.52</v>
+        <v>3891539.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>河北世鸿餐饮管理有限公司</t>
+          <t>河北金怡化纤有限公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -69504,31 +69504,31 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>177304.59</v>
+        <v>141747.53</v>
       </c>
       <c r="F5" t="n">
-        <v>84310.64</v>
+        <v>69702.14</v>
       </c>
       <c r="G5" t="n">
-        <v>9295.639999999999</v>
+        <v>977.5</v>
       </c>
       <c r="H5" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>310529.88</v>
+        <v>421107.52</v>
       </c>
       <c r="K5" t="n">
-        <v>3950529.88</v>
+        <v>4061107.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>河北产投金财合成股权投资基金合伙企业（有限合伙）</t>
+          <t>河北军存预拌混凝土有限公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -69543,31 +69543,31 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>449479.72</v>
+        <v>175912.65</v>
       </c>
       <c r="F6" t="n">
-        <v>6345.07</v>
+        <v>17454.88</v>
       </c>
       <c r="G6" t="n">
-        <v>6345.07</v>
+        <v>10.95</v>
       </c>
       <c r="H6" t="n">
-        <v>107</v>
+        <v>308</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>859239.4400000001</v>
+        <v>787804.8900000001</v>
       </c>
       <c r="K6" t="n">
-        <v>4499239.439999999</v>
+        <v>4427804.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>河北建投钒晟储能科技有限公司</t>
+          <t>河北世鸿餐饮管理有限公司</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -69582,65 +69582,75 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>2772593.05</v>
+        <v>177304.59</v>
       </c>
       <c r="F7" t="n">
-        <v>3859.09</v>
+        <v>84310.64</v>
       </c>
       <c r="G7" t="n">
-        <v>3775.6</v>
+        <v>9295.639999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>239</v>
+        <v>154</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>879210.7699999999</v>
+        <v>310529.88</v>
       </c>
       <c r="K7" t="n">
-        <v>4519210.77</v>
+        <v>3950529.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>石家庄一建建设集团有限公司</t>
+          <t>石家庄市陆升水处理设备有限公司</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3754825.42</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>128169.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>82160.38</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5275.41</v>
+      </c>
       <c r="H8" t="n">
-        <v>365</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="I8" t="n">
+        <v>23</v>
+      </c>
+      <c r="J8" t="n">
+        <v>329601.93</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3969601.93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>河北钜亨环境工程有限公司</t>
+          <t>河北产投金财合成股权投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -69650,65 +69660,75 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>623371.36</v>
+        <v>449479.72</v>
       </c>
       <c r="F9" t="n">
-        <v>429.02</v>
+        <v>6345.07</v>
       </c>
       <c r="G9" t="n">
-        <v>429.02</v>
+        <v>6345.07</v>
       </c>
       <c r="H9" t="n">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>906567.84</v>
+        <v>859239.4400000001</v>
       </c>
       <c r="K9" t="n">
-        <v>4546567.840000001</v>
+        <v>4499239.439999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>河北住建绿色建筑科技有限公司</t>
+          <t>河北建投钒晟储能科技有限公司</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1775155.6</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>2772593.05</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3859.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3775.6</v>
+      </c>
       <c r="H10" t="n">
-        <v>190</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>879210.7699999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4519210.77</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>河北杰安建筑安装工程有限公司</t>
+          <t>河北博斯特展览服务有限公司</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -69718,60 +69738,70 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>335361.9</v>
+        <v>273867.56</v>
       </c>
       <c r="F11" t="n">
-        <v>4060.06</v>
+        <v>73759.55</v>
       </c>
       <c r="G11" t="n">
-        <v>4060.06</v>
+        <v>201805.43</v>
       </c>
       <c r="H11" t="n">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>877519.52</v>
+        <v>191877.72</v>
       </c>
       <c r="K11" t="n">
-        <v>4517519.52</v>
+        <v>3831877.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>石家庄绿环新能源科技有限公司正定分公司</t>
+          <t>河北尚凯工程项目管理有限公司</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>225123.5</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+        <v>305189.75</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6025.93</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6071.52</v>
+      </c>
       <c r="H12" t="n">
-        <v>201</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+        <v>208</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>861746.97</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4501746.970000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>新疆燕翔实业发展有限公司</t>
+          <t>邢台市金成航冶金轧辊有限公司</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -69786,31 +69816,31 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>134066.34</v>
+        <v>226387.87</v>
       </c>
       <c r="F13" t="n">
-        <v>94220.10000000001</v>
+        <v>30737.8</v>
       </c>
       <c r="G13" t="n">
-        <v>140748.79</v>
+        <v>28655.98</v>
       </c>
       <c r="H13" t="n">
-        <v>283</v>
+        <v>155</v>
       </c>
       <c r="I13" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>109710.51</v>
+        <v>666179.42</v>
       </c>
       <c r="K13" t="n">
-        <v>3749710.51</v>
+        <v>4306179.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>邢台市金成航冶金轧辊有限公司</t>
+          <t>新疆燕翔实业发展有限公司</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -69825,31 +69855,31 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>226387.87</v>
+        <v>134066.34</v>
       </c>
       <c r="F14" t="n">
-        <v>30737.8</v>
+        <v>94220.10000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>28655.98</v>
+        <v>140748.79</v>
       </c>
       <c r="H14" t="n">
-        <v>155</v>
+        <v>283</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J14" t="n">
-        <v>666179.42</v>
+        <v>109710.51</v>
       </c>
       <c r="K14" t="n">
-        <v>4306179.42</v>
+        <v>3749710.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>中科电谷（北京）系统技术有限公司</t>
+          <t>河北住建绿色建筑科技有限公司</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -69858,37 +69888,27 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>230338.19</v>
-      </c>
-      <c r="F15" t="n">
-        <v>74779.23</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1061777.01</v>
-      </c>
+        <v>1775155.6</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>120</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-675231.62</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2964768.38</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河北佰汀商贸有限公司</t>
+          <t>河北杰安建筑安装工程有限公司</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -69903,31 +69923,31 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>655363.9399999999</v>
+        <v>335361.9</v>
       </c>
       <c r="F16" t="n">
-        <v>53932.2</v>
+        <v>4060.06</v>
       </c>
       <c r="G16" t="n">
-        <v>417.61</v>
+        <v>4060.06</v>
       </c>
       <c r="H16" t="n">
-        <v>210</v>
+        <v>134</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>532056.99</v>
+        <v>877519.52</v>
       </c>
       <c r="K16" t="n">
-        <v>4172056.99</v>
+        <v>4517519.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>石家庄振鹏电器有限公司</t>
+          <t>河北钜亨环境工程有限公司</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -69942,31 +69962,31 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>152006.41</v>
+        <v>623371.36</v>
       </c>
       <c r="F17" t="n">
-        <v>2864.9</v>
+        <v>429.02</v>
       </c>
       <c r="G17" t="n">
-        <v>2776.49</v>
+        <v>429.02</v>
       </c>
       <c r="H17" t="n">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>887169.21</v>
+        <v>906567.84</v>
       </c>
       <c r="K17" t="n">
-        <v>4527169.21</v>
+        <v>4546567.840000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>河北玖华通信科技集团有限公司</t>
+          <t>石家庄绿环新能源科技有限公司正定分公司</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -69975,37 +69995,27 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>150621.3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1412.79</v>
-      </c>
-      <c r="G18" t="n">
-        <v>627.8200000000001</v>
-      </c>
+        <v>225123.5</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>131</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>899482.65</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4539482.65</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>石家庄明式空间艺术建筑装饰有限公司</t>
+          <t>中科电谷（北京）系统技术有限公司</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -70020,31 +70030,31 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>126288.16</v>
+        <v>230338.19</v>
       </c>
       <c r="F19" t="n">
-        <v>135.07</v>
+        <v>74779.23</v>
       </c>
       <c r="G19" t="n">
-        <v>135.07</v>
+        <v>1061777.01</v>
       </c>
       <c r="H19" t="n">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>908919.4400000001</v>
+        <v>-675231.62</v>
       </c>
       <c r="K19" t="n">
-        <v>4548919.439999999</v>
+        <v>2964768.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>河北明德澄道艺术品评估有限责任公司</t>
+          <t>石家庄一建建设集团有限公司</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -70053,37 +70063,27 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>139900.16</v>
-      </c>
-      <c r="F20" t="n">
-        <v>18288.69</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6365.89</v>
-      </c>
+        <v>3754825.42</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>140</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>775613.28</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4415613.28</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>河北恒青电子科技有限公司</t>
+          <t>石家庄振鹏电器有限公司</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -70098,31 +70098,31 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>139230.75</v>
+        <v>152006.41</v>
       </c>
       <c r="F21" t="n">
-        <v>59982.81</v>
+        <v>2864.9</v>
       </c>
       <c r="G21" t="n">
-        <v>56090.87</v>
+        <v>2776.49</v>
       </c>
       <c r="H21" t="n">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>434029.46</v>
+        <v>887169.21</v>
       </c>
       <c r="K21" t="n">
-        <v>4074029.459999999</v>
+        <v>4527169.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>河北易昆企业管理咨询有限公司</t>
+          <t>石家庄明式空间艺术建筑装饰有限公司</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -70137,31 +70137,31 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>392986.85</v>
+        <v>126288.16</v>
       </c>
       <c r="F22" t="n">
-        <v>84533.14</v>
+        <v>135.07</v>
       </c>
       <c r="G22" t="n">
-        <v>88060.87</v>
+        <v>135.07</v>
       </c>
       <c r="H22" t="n">
-        <v>365</v>
+        <v>189</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>230207.15</v>
+        <v>908919.4400000001</v>
       </c>
       <c r="K22" t="n">
-        <v>3870207.15</v>
+        <v>4548919.439999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>河北冀快商贸有限公司</t>
+          <t>河北明德澄道艺术品评估有限责任公司</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -70176,36 +70176,36 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>272299.59</v>
+        <v>139900.16</v>
       </c>
       <c r="F23" t="n">
-        <v>6216.66</v>
+        <v>18288.69</v>
       </c>
       <c r="G23" t="n">
-        <v>1641.02</v>
+        <v>6365.89</v>
       </c>
       <c r="H23" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>864842.3600000001</v>
+        <v>775613.28</v>
       </c>
       <c r="K23" t="n">
-        <v>4504842.36</v>
+        <v>4415613.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>冀州中意复合材料股份有限公司</t>
+          <t>河北玖华通信科技集团有限公司</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -70215,36 +70215,36 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>130030.97</v>
+        <v>150621.3</v>
       </c>
       <c r="F24" t="n">
-        <v>291.04</v>
+        <v>1412.79</v>
       </c>
       <c r="G24" t="n">
-        <v>291.04</v>
+        <v>627.8200000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>237</v>
+        <v>131</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>907671.6799999999</v>
+        <v>899482.65</v>
       </c>
       <c r="K24" t="n">
-        <v>4547671.680000001</v>
+        <v>4539482.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>石家庄江建电气安装有限公司</t>
+          <t>河北恒青电子科技有限公司</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -70254,36 +70254,36 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>174002.91</v>
+        <v>139230.75</v>
       </c>
       <c r="F25" t="n">
-        <v>60146.34</v>
+        <v>59982.81</v>
       </c>
       <c r="G25" t="n">
-        <v>105764.46</v>
+        <v>56090.87</v>
       </c>
       <c r="H25" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>383211.16</v>
+        <v>434029.46</v>
       </c>
       <c r="K25" t="n">
-        <v>4023211.16</v>
+        <v>4074029.459999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>石家庄君莫笑餐饮管理有限公司</t>
+          <t>河北易昆企业管理咨询有限公司</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -70293,36 +70293,36 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>130634.2</v>
+        <v>392986.85</v>
       </c>
       <c r="F26" t="n">
-        <v>13691.8</v>
+        <v>84533.14</v>
       </c>
       <c r="G26" t="n">
-        <v>5176.35</v>
+        <v>88060.87</v>
       </c>
       <c r="H26" t="n">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>808981.05</v>
+        <v>230207.15</v>
       </c>
       <c r="K26" t="n">
-        <v>4448981.050000001</v>
+        <v>3870207.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>河北瑞星燃气设备股份有限公司</t>
+          <t>河北佰汀商贸有限公司</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -70332,36 +70332,36 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>458376.12</v>
+        <v>655363.9399999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>53932.2</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>417.61</v>
       </c>
       <c r="H27" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>910000</v>
+        <v>532056.99</v>
       </c>
       <c r="K27" t="n">
-        <v>4550000</v>
+        <v>4172056.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>河北华曙新能源汽车科技有限公司</t>
+          <t>河北冀快商贸有限公司</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -70371,31 +70371,31 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>194439.82</v>
+        <v>272299.59</v>
       </c>
       <c r="F28" t="n">
-        <v>98861</v>
+        <v>6216.66</v>
       </c>
       <c r="G28" t="n">
-        <v>41781.81</v>
+        <v>1641.02</v>
       </c>
       <c r="H28" t="n">
-        <v>116</v>
+        <v>280</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>176191.19</v>
+        <v>864842.3600000001</v>
       </c>
       <c r="K28" t="n">
-        <v>3816191.19</v>
+        <v>4504842.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>河北盈前人力资源服务有限公司</t>
+          <t>冀州中意复合材料股份有限公司</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -70410,31 +70410,31 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>399407.34</v>
+        <v>130030.97</v>
       </c>
       <c r="F29" t="n">
-        <v>36696.99</v>
+        <v>291.04</v>
       </c>
       <c r="G29" t="n">
-        <v>35151.88</v>
+        <v>291.04</v>
       </c>
       <c r="H29" t="n">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>617969.1900000001</v>
+        <v>907671.6799999999</v>
       </c>
       <c r="K29" t="n">
-        <v>4257969.19</v>
+        <v>4547671.680000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>河北星源密封件集团有限公司</t>
+          <t>石家庄君莫笑餐饮管理有限公司</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -70449,25 +70449,25 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>367599.86</v>
+        <v>130634.2</v>
       </c>
       <c r="F30" t="n">
-        <v>68916.60000000001</v>
+        <v>13691.8</v>
       </c>
       <c r="G30" t="n">
-        <v>44422.78</v>
+        <v>5176.35</v>
       </c>
       <c r="H30" t="n">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>383161.02</v>
+        <v>808981.05</v>
       </c>
       <c r="K30" t="n">
-        <v>4023161.02</v>
+        <v>4448981.050000001</v>
       </c>
     </row>
     <row r="31">
@@ -70551,12 +70551,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>石家庄筑登装饰工程有限公司</t>
+          <t>河北星源密封件集团有限公司</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>邸平花</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -70566,36 +70566,36 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>110448.33</v>
+        <v>367599.86</v>
       </c>
       <c r="F33" t="n">
-        <v>47721.04</v>
+        <v>68916.60000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>25283.09</v>
+        <v>44422.78</v>
       </c>
       <c r="H33" t="n">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>550669.63</v>
+        <v>383161.02</v>
       </c>
       <c r="K33" t="n">
-        <v>4190669.630000001</v>
+        <v>4023161.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>河北尚凯工程项目管理有限公司</t>
+          <t>河北盈前人力资源服务有限公司</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -70605,36 +70605,36 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>305189.75</v>
+        <v>399407.34</v>
       </c>
       <c r="F34" t="n">
-        <v>6025.93</v>
+        <v>36696.99</v>
       </c>
       <c r="G34" t="n">
-        <v>6071.52</v>
+        <v>35151.88</v>
       </c>
       <c r="H34" t="n">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>861746.97</v>
+        <v>617969.1900000001</v>
       </c>
       <c r="K34" t="n">
-        <v>4501746.970000001</v>
+        <v>4257969.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>河北博斯特展览服务有限公司</t>
+          <t>河北华曙新能源汽车科技有限公司</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -70644,36 +70644,36 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>273867.56</v>
+        <v>194439.82</v>
       </c>
       <c r="F35" t="n">
-        <v>73759.55</v>
+        <v>98861</v>
       </c>
       <c r="G35" t="n">
-        <v>201805.43</v>
+        <v>41781.81</v>
       </c>
       <c r="H35" t="n">
-        <v>240</v>
+        <v>116</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>191877.72</v>
+        <v>176191.19</v>
       </c>
       <c r="K35" t="n">
-        <v>3831877.72</v>
+        <v>3816191.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>石家庄市陆升水处理设备有限公司</t>
+          <t>河北瑞星燃气设备股份有限公司</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -70683,36 +70683,36 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>128169.9</v>
+        <v>458376.12</v>
       </c>
       <c r="F36" t="n">
-        <v>82160.38</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>5275.41</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>329601.93</v>
+        <v>910000</v>
       </c>
       <c r="K36" t="n">
-        <v>3969601.93</v>
+        <v>4550000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>河北军存预拌混凝土有限公司</t>
+          <t>石家庄江建电气安装有限公司</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -70722,36 +70722,36 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>175912.65</v>
+        <v>174002.91</v>
       </c>
       <c r="F37" t="n">
-        <v>17454.88</v>
+        <v>60146.34</v>
       </c>
       <c r="G37" t="n">
-        <v>10.95</v>
+        <v>105764.46</v>
       </c>
       <c r="H37" t="n">
-        <v>308</v>
+        <v>102</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>787804.8900000001</v>
+        <v>383211.16</v>
       </c>
       <c r="K37" t="n">
-        <v>4427804.89</v>
+        <v>4023211.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>河北仁恒工程管理服务有限公司</t>
+          <t>石家庄筑登装饰工程有限公司</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>邸平花</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -70761,25 +70761,25 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>172758.08</v>
+        <v>110448.33</v>
       </c>
       <c r="F38" t="n">
-        <v>82215.39999999999</v>
+        <v>47721.04</v>
       </c>
       <c r="G38" t="n">
-        <v>82952.86</v>
+        <v>25283.09</v>
       </c>
       <c r="H38" t="n">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>251539.34</v>
+        <v>550669.63</v>
       </c>
       <c r="K38" t="n">
-        <v>3891539.34</v>
+        <v>4190669.630000001</v>
       </c>
     </row>
   </sheetData>
@@ -72141,7 +72141,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>河北有朴建筑装饰工程有限公司</t>
+          <t>宏鑫电缆有限公司</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -72153,31 +72153,31 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>75633.73</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>226168.35</v>
+        <v>274138.45</v>
       </c>
       <c r="F36" t="n">
-        <v>523106.99</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>-1196285.44</v>
+        <v>-1008969.15</v>
       </c>
       <c r="J36" t="n">
-        <v>2443714.56</v>
+        <v>2631030.85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>围场满族蒙古族自治县塞韵光伏发电有限责任公司</t>
+          <t>河北有朴建筑装饰工程有限公司</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -72189,31 +72189,31 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>69597.42</v>
+        <v>75633.73</v>
       </c>
       <c r="E37" t="n">
-        <v>272326.64</v>
+        <v>226168.35</v>
       </c>
       <c r="F37" t="n">
-        <v>4093.86</v>
+        <v>523106.99</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I37" t="n">
-        <v>-1000380.34</v>
+        <v>-1196285.44</v>
       </c>
       <c r="J37" t="n">
-        <v>2639619.66</v>
+        <v>2443714.56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>河北欣康投资有限公司</t>
+          <t>围场满族蒙古族自治县塞韵光伏发电有限责任公司</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -72225,31 +72225,31 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>69597.42</v>
       </c>
       <c r="E38" t="n">
-        <v>544409.64</v>
+        <v>272326.64</v>
       </c>
       <c r="F38" t="n">
-        <v>834352.49</v>
+        <v>4093.86</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>-3735219.970000001</v>
+        <v>-1000380.34</v>
       </c>
       <c r="J38" t="n">
-        <v>-95219.97000000044</v>
+        <v>2639619.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>河北世翔密封件有限公司</t>
+          <t>河北欣康投资有限公司</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -72261,31 +72261,31 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>311433.26</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>396004.32</v>
+        <v>544409.64</v>
       </c>
       <c r="F39" t="n">
-        <v>30682.98</v>
+        <v>834352.49</v>
       </c>
       <c r="G39" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I39" t="n">
-        <v>-1892713.22</v>
+        <v>-3735219.970000001</v>
       </c>
       <c r="J39" t="n">
-        <v>1747286.78</v>
+        <v>-95219.97000000044</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>河北绿诺食品有限公司</t>
+          <t>河北世翔密封件有限公司</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -72297,31 +72297,31 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>163268.24</v>
+        <v>311433.26</v>
       </c>
       <c r="E40" t="n">
-        <v>1123362.75</v>
+        <v>396004.32</v>
       </c>
       <c r="F40" t="n">
-        <v>257265.7</v>
+        <v>30682.98</v>
       </c>
       <c r="G40" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="H40" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>-7210804.95</v>
+        <v>-1892713.22</v>
       </c>
       <c r="J40" t="n">
-        <v>-3570804.95</v>
+        <v>1747286.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>河北金柳化纤有限公司</t>
+          <t>河北绿诺食品有限公司</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -72333,61 +72333,61 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>643.25</v>
+        <v>163268.24</v>
       </c>
       <c r="E41" t="n">
-        <v>205757</v>
+        <v>1123362.75</v>
       </c>
       <c r="F41" t="n">
-        <v>205757</v>
+        <v>257265.7</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H41" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="I41" t="n">
-        <v>-736056</v>
+        <v>-7210804.95</v>
       </c>
       <c r="J41" t="n">
-        <v>2903944</v>
+        <v>-3570804.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>宏鑫电缆有限公司</t>
+          <t>河北金柳化纤有限公司</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>643.25</v>
       </c>
       <c r="E42" t="n">
-        <v>274138.45</v>
+        <v>205757</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>205757</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="I42" t="n">
-        <v>-1008969.15</v>
+        <v>-736056</v>
       </c>
       <c r="J42" t="n">
-        <v>2631030.85</v>
+        <v>2903944</v>
       </c>
     </row>
   </sheetData>
